--- a/docs/reference/interfaces/接口列表.xlsx
+++ b/docs/reference/interfaces/接口列表.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="389">
   <si>
     <t>系统</t>
   </si>
@@ -64,6 +64,9 @@
     <t>对于功能改造</t>
   </si>
   <si>
+    <t>对于HIS对象</t>
+  </si>
+  <si>
     <t>说明：上传，回传，修改等接口是HIS提供视图数据。</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>/ehr/v1.0/sys</t>
   </si>
   <si>
+    <t>是否每次调用中间接口在 his库都存非结构化（xml，json）的日志数据？</t>
+  </si>
+  <si>
     <t>查询本机构用户列表</t>
   </si>
   <si>
@@ -148,6 +154,9 @@
     <t>中间接口 + 数据库（视图）+ 前台界面</t>
   </si>
   <si>
+    <t>V_四川_健康档案云_723_上传健康档案</t>
+  </si>
+  <si>
     <t>修改健康档案</t>
   </si>
   <si>
@@ -178,6 +187,13 @@
     <t>/ehr/v1.0/lnrgl</t>
   </si>
   <si>
+    <t>V_四川_健康档案云_731_上传健康体检
+V_四川_健康档案云_731_上传健康体检_FMYDATA</t>
+  </si>
+  <si>
+    <t>这个上传里面有多个数组数据，应该对数组数据在建单独视图吗？</t>
+  </si>
+  <si>
     <t>修改健康体检</t>
   </si>
   <si>
@@ -295,12 +311,18 @@
     <t>100-003</t>
   </si>
   <si>
+    <t>基卫_综合目录</t>
+  </si>
+  <si>
     <t>三大目录（药品、诊疗、耗材）</t>
   </si>
   <si>
     <t>100-004</t>
   </si>
   <si>
+    <t>基卫_三大目录</t>
+  </si>
+  <si>
     <t>三大目录（药品、诊疗、耗材）行数</t>
   </si>
   <si>
@@ -313,6 +335,9 @@
     <t>100-006</t>
   </si>
   <si>
+    <t>基卫_诊断数据</t>
+  </si>
+  <si>
     <t>诊断行数</t>
   </si>
   <si>
@@ -325,6 +350,9 @@
     <t>100-008</t>
   </si>
   <si>
+    <t>基卫_医疗机构信息</t>
+  </si>
+  <si>
     <t>单点登录</t>
   </si>
   <si>
@@ -436,12 +464,18 @@
     <t>HIS系统调用中间接口 + HIS提供视图数据</t>
   </si>
   <si>
+    <t>基卫_住院病人信息</t>
+  </si>
+  <si>
     <t>获取门诊患者个案信息</t>
   </si>
   <si>
     <t>300-002</t>
   </si>
   <si>
+    <t>基卫_门诊病人信息</t>
+  </si>
+  <si>
     <t>接收上级转诊</t>
   </si>
   <si>
@@ -523,12 +557,18 @@
     <t>中间接口 + 前台改造</t>
   </si>
   <si>
+    <t>基卫_检查项目（以类型字段 区分LIS PACS 心电）</t>
+  </si>
+  <si>
     <t>按申请单号获取申请单</t>
   </si>
   <si>
     <t>500-002</t>
   </si>
   <si>
+    <t>基卫_检查申请单（以类型字段 区分LIS PACS 心电）</t>
+  </si>
+  <si>
     <t>回写报告</t>
   </si>
   <si>
@@ -536,6 +576,9 @@
   </si>
   <si>
     <t>中间接口 + 前台改造 + 数据库</t>
+  </si>
+  <si>
+    <t>V_四川_基卫_回写报告</t>
   </si>
   <si>
     <t>LIS 系统</t>
@@ -2305,7 +2348,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2359,6 +2402,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2487,7 +2533,7 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="0" dbFileVersion="0" changeLogVersion="0">
-    <open main="35" threadCnt="1"/>
+    <open main="37" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="0" sheetStid="1">
         <open main="1" threadCnt="1"/>
@@ -2753,7 +2799,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15.7" customWidth="1"/>
@@ -2763,10 +2809,10 @@
     <col min="6" max="7" width="9.875" customWidth="1"/>
     <col min="8" max="8" width="10.7583333333333" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="43.75" customWidth="1"/>
+    <col min="10" max="11" width="43.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:11">
+    <row r="1" ht="14.25" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2797,1596 +2843,1676 @@
       <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:12">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" spans="1:11">
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" spans="1:12">
       <c r="A3" s="9"/>
       <c r="B3" s="10"/>
       <c r="C3" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:11">
+        <v>18</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:12">
       <c r="A4" s="9"/>
       <c r="B4" s="13"/>
       <c r="C4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>22</v>
-      </c>
       <c r="G4" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:12">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:11">
+        <v>33</v>
+      </c>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="9"/>
       <c r="B6" s="10"/>
       <c r="C6" s="14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="1:11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:12">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="9"/>
       <c r="B9" s="13"/>
       <c r="C9" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" spans="1:11">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="27.75" spans="1:12">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="1:12">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:12">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>47</v>
-      </c>
       <c r="G12" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H12">
         <v>99</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="9"/>
       <c r="B13" s="13"/>
-      <c r="C13" s="18" t="s">
-        <v>53</v>
+      <c r="C13" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H13">
         <v>99</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:12">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="D14" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>57</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>52</v>
       </c>
       <c r="H14">
         <v>99</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:12">
       <c r="A15" s="9"/>
       <c r="B15" s="13"/>
-      <c r="C15" s="18" t="s">
-        <v>59</v>
+      <c r="C15" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H15">
         <v>99</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:12">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H16">
         <v>99</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:10">
+        <v>39</v>
+      </c>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" ht="14.25" spans="1:11">
       <c r="A17" s="9"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>40</v>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H17">
         <v>99</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:10">
+        <v>39</v>
+      </c>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" ht="14.25" spans="1:11">
       <c r="A18" s="9"/>
-      <c r="B18" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>70</v>
+      <c r="B18" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="1:11">
       <c r="A19" s="9"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>70</v>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" spans="1:11">
       <c r="A20" s="9"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>70</v>
+      <c r="B20" s="23"/>
+      <c r="C20" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="1:11">
       <c r="A21" s="9"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23" t="s">
+      <c r="B21" s="23"/>
+      <c r="C21" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>70</v>
-      </c>
       <c r="G21" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" spans="1:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" spans="1:11">
       <c r="A22" s="9"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>70</v>
+      <c r="B22" s="26"/>
+      <c r="C22" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:10">
-      <c r="A23" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="1:11">
+      <c r="A23" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:10">
-      <c r="A24" s="26"/>
-      <c r="B24" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28" t="s">
-        <v>29</v>
+      <c r="D23" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+    </row>
+    <row r="24" ht="14.25" spans="1:11">
+      <c r="A24" s="27"/>
+      <c r="B24" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H24">
         <v>99</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="1:10">
-      <c r="A25" s="26"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="1:11">
+      <c r="A25" s="27"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H25">
         <v>99</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" ht="27.75" spans="1:10">
-      <c r="A26" s="26"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" ht="27.75" spans="1:11">
+      <c r="A26" s="27"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H26">
         <v>99</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J26" s="8"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="1:10">
-      <c r="A27" s="26"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28" t="s">
-        <v>29</v>
+      <c r="K26" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:11">
+      <c r="A27" s="27"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H27">
         <v>99</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J27" s="8"/>
-    </row>
-    <row r="28" ht="14.25" spans="1:10">
-      <c r="A28" s="26"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28" t="s">
-        <v>29</v>
+      <c r="K27" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" spans="1:11">
+      <c r="A28" s="27"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H28">
         <v>99</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="8"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:10">
-      <c r="A29" s="26"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28" t="s">
-        <v>29</v>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:11">
+      <c r="A29" s="27"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H29">
         <v>99</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J29" s="8"/>
-    </row>
-    <row r="30" ht="14.25" spans="1:10">
-      <c r="A30" s="26"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28" t="s">
-        <v>29</v>
+      <c r="K29" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" spans="1:11">
+      <c r="A30" s="27"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H30">
         <v>99</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J30" s="8"/>
-    </row>
-    <row r="31" ht="14.25" spans="1:10">
-      <c r="A31" s="26"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28" t="s">
-        <v>29</v>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31" ht="14.25" spans="1:11">
+      <c r="A31" s="27"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H31">
         <v>99</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J31" s="8"/>
-    </row>
-    <row r="32" ht="14.25" spans="1:10">
-      <c r="A32" s="26"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28" t="s">
-        <v>29</v>
+      <c r="K31" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" spans="1:11">
+      <c r="A32" s="27"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H32">
         <v>99</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J32" s="8"/>
-    </row>
-    <row r="33" ht="14.25" spans="1:9">
-      <c r="A33" s="26"/>
-      <c r="B33" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" spans="1:9">
-      <c r="A34" s="26"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" spans="1:9">
-      <c r="A35" s="26"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:9">
-      <c r="A36" s="26"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:9">
-      <c r="A37" s="26"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="31" t="s">
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" ht="14.25" spans="1:11">
+      <c r="A33" s="27"/>
+      <c r="B33" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="C33" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:9">
-      <c r="A38" s="26"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="31" t="s">
+      <c r="D33" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" spans="1:11">
+      <c r="A34" s="27"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:9">
-      <c r="A39" s="26"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="31" t="s">
+      <c r="D34" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" spans="1:11">
+      <c r="A35" s="27"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" spans="1:9">
-      <c r="A40" s="26"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="31" t="s">
+      <c r="D35" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:11">
+      <c r="A36" s="27"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" spans="1:9">
-      <c r="A41" s="26"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="31" t="s">
+      <c r="D36" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" spans="1:11">
+      <c r="A37" s="27"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" spans="1:9">
-      <c r="A42" s="26"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="31" t="s">
+      <c r="D37" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" spans="1:11">
+      <c r="A38" s="27"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" spans="1:9">
-      <c r="A43" s="26"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="31" t="s">
+      <c r="D38" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:11">
+      <c r="A39" s="27"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" spans="1:9">
-      <c r="A44" s="26"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="31" t="s">
+      <c r="D39" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" spans="1:11">
+      <c r="A40" s="27"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" spans="1:9">
-      <c r="A45" s="26"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="31" t="s">
+      <c r="D40" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="31" t="s">
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" spans="1:11">
+      <c r="A41" s="27"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:9">
-      <c r="A46" s="26"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="31" t="s">
+      <c r="D41" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" spans="1:11">
+      <c r="A42" s="27"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" spans="1:9">
-      <c r="A47" s="26"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="31" t="s">
+      <c r="D42" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" spans="1:11">
+      <c r="A43" s="27"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" spans="1:9">
-      <c r="A48" s="26"/>
-      <c r="B48" s="33" t="s">
+      <c r="D43" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="31" t="s">
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:11">
+      <c r="A44" s="27"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="31" t="s">
+      <c r="D44" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28" t="s">
-        <v>29</v>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" spans="1:11">
+      <c r="A45" s="27"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:11">
+      <c r="A46" s="27"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" spans="1:11">
+      <c r="A47" s="27"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" spans="1:11">
+      <c r="A48" s="27"/>
+      <c r="B48" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H48">
         <v>3</v>
       </c>
       <c r="I48" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" spans="1:10">
-      <c r="A49" s="26"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28" t="s">
-        <v>29</v>
+        <v>142</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="1:11">
+      <c r="A49" s="27"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H49">
         <v>3</v>
       </c>
       <c r="I49" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" ht="14.25" spans="1:10">
-      <c r="A50" s="26"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28" t="s">
-        <v>29</v>
+        <v>142</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25" spans="1:11">
+      <c r="A50" s="27"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H50">
         <v>3</v>
       </c>
       <c r="I50" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25" spans="1:10">
-      <c r="A51" s="26"/>
-      <c r="B51" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="D51" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28" t="s">
-        <v>29</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25" spans="1:11">
+      <c r="A51" s="27"/>
+      <c r="B51" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H51">
         <v>2</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J51" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" spans="1:11">
+      <c r="A52" s="27"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D52" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="52" ht="14.25" spans="1:10">
-      <c r="A52" s="26"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D52" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H52">
         <v>2</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J52" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:11">
+      <c r="A53" s="27"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+    </row>
+    <row r="54" ht="14.25" spans="1:11">
+      <c r="A54" s="27"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" spans="1:10">
-      <c r="A53" s="26"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D53" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="J53" s="8"/>
-    </row>
-    <row r="54" ht="14.25" spans="1:10">
-      <c r="A54" s="26"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H54">
         <v>2</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J54" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K54" s="8"/>
+    </row>
+    <row r="55" ht="14.25" spans="1:11">
+      <c r="A55" s="27"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25" spans="1:10">
-      <c r="A55" s="26"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H55">
         <v>2</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J55" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K55" s="8"/>
+    </row>
+    <row r="56" ht="14.25" spans="1:11">
+      <c r="A56" s="27"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25" spans="1:10">
-      <c r="A56" s="26"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H56">
         <v>2</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J56" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K56" s="8"/>
+    </row>
+    <row r="57" ht="14.25" spans="1:11">
+      <c r="A57" s="27"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="57" ht="14.25" spans="1:10">
-      <c r="A57" s="26"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="D57" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H57">
         <v>2</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J57" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K57" s="8"/>
+    </row>
+    <row r="58" ht="14.25" spans="1:11">
+      <c r="A58" s="27"/>
+      <c r="B58" s="34"/>
+      <c r="C58" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" spans="1:10">
-      <c r="A58" s="26"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="D58" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H58">
         <v>2</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J58" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K58" s="8"/>
+    </row>
+    <row r="59" ht="14.25" spans="1:11">
+      <c r="A59" s="27"/>
+      <c r="B59" s="34"/>
+      <c r="C59" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25" spans="1:10">
-      <c r="A59" s="26"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D59" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H59">
         <v>2</v>
       </c>
       <c r="I59" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J59" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K59" s="8"/>
+    </row>
+    <row r="60" ht="14.25" spans="1:11">
+      <c r="A60" s="27"/>
+      <c r="B60" s="34"/>
+      <c r="C60" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="60" ht="14.25" spans="1:10">
-      <c r="A60" s="26"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="D60" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H60">
         <v>2</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J60" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K60" s="8"/>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="27"/>
+      <c r="B61" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C61" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="61" ht="14.25" spans="1:10">
-      <c r="A61" s="26"/>
-      <c r="B61" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="C61" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="D61" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="62" ht="14.25" spans="1:10">
-      <c r="A62" s="26"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28" t="s">
-        <v>29</v>
+        <v>173</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" spans="1:11">
+      <c r="A62" s="27"/>
+      <c r="B62" s="34"/>
+      <c r="C62" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J62" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="63" ht="14.25" spans="1:10">
-      <c r="A63" s="26"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="D63" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37" t="s">
-        <v>29</v>
+        <v>173</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="63" ht="14.25" spans="1:11">
+      <c r="A63" s="27"/>
+      <c r="B63" s="34"/>
+      <c r="C63" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38" t="s">
+        <v>31</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="64" ht="14.25" spans="1:10">
-      <c r="A64" s="26"/>
-      <c r="B64" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="C64" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="D64" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28" t="s">
-        <v>29</v>
+        <v>180</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" ht="14.25" spans="1:11">
+      <c r="A64" s="27"/>
+      <c r="B64" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="65" ht="14.25" spans="1:10">
-      <c r="A65" s="26"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="D65" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28" t="s">
-        <v>29</v>
+        <v>180</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25" spans="1:11">
+      <c r="A65" s="27"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="29"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="66" ht="14.25" spans="1:10">
-      <c r="A66" s="26"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="D66" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37" t="s">
-        <v>29</v>
+        <v>180</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25" spans="1:11">
+      <c r="A66" s="27"/>
+      <c r="B66" s="34"/>
+      <c r="C66" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38" t="s">
+        <v>31</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="67" ht="14.25" spans="1:10">
-      <c r="A67" s="26"/>
-      <c r="B67" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C67" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="D67" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28" t="s">
-        <v>29</v>
+        <v>180</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25" spans="1:11">
+      <c r="A67" s="27"/>
+      <c r="B67" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C67" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="68" ht="14.25" spans="1:10">
-      <c r="A68" s="26"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="D68" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28" t="s">
-        <v>29</v>
+        <v>180</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25" spans="1:11">
+      <c r="A68" s="27"/>
+      <c r="B68" s="34"/>
+      <c r="C68" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="69" ht="14.25" spans="1:10">
-      <c r="A69" s="26"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="K68" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="36" t="s">
-        <v>178</v>
-      </c>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37" t="s">
-        <v>29</v>
+    </row>
+    <row r="69" ht="14.25" spans="1:11">
+      <c r="A69" s="27"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38" t="s">
+        <v>31</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="70" ht="14.25" spans="1:10">
-      <c r="A70" s="26"/>
-      <c r="B70" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="C70" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="D70" s="31" t="s">
+      <c r="K69" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="71" ht="14.25" spans="1:10">
-      <c r="A71" s="26"/>
-      <c r="B71" s="33"/>
-      <c r="C71" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="D71" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" ht="14.25" spans="1:10">
-      <c r="A72" s="26"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="D72" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" ht="14.25" spans="1:10">
-      <c r="A73" s="26"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="D73" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" ht="14.25" spans="1:10">
-      <c r="A74" s="26"/>
-      <c r="B74" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="C74" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D74" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
-      <c r="G74" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="75" ht="14.25" spans="1:10">
-      <c r="A75" s="26"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D75" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="76" ht="14.25" spans="1:10">
-      <c r="A76" s="26"/>
-      <c r="B76" s="33"/>
-      <c r="C76" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="D76" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+    </row>
+    <row r="70" ht="14.25" spans="1:11">
+      <c r="A70" s="27"/>
+      <c r="B70" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25" spans="1:11">
+      <c r="A71" s="27"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25" spans="1:11">
+      <c r="A72" s="27"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25" spans="1:11">
+      <c r="A73" s="27"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="E73" s="29"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" ht="14.25" spans="1:11">
+      <c r="A74" s="27"/>
+      <c r="B74" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D74" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E74" s="29"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" ht="14.25" spans="1:11">
+      <c r="A75" s="27"/>
+      <c r="B75" s="34"/>
+      <c r="C75" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="E75" s="29"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" ht="14.25" spans="1:11">
+      <c r="A76" s="27"/>
+      <c r="B76" s="34"/>
+      <c r="C76" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="D76" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="B77" s="6" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H77" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L77" etc:filterBottomFollowUsedRange="1">
     <extLst/>
   </autoFilter>
   <mergeCells count="17">
@@ -4435,16 +4561,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="E2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="2:6">
@@ -4452,16 +4578,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" ht="39" spans="2:6">
@@ -4469,16 +4595,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="E4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" ht="39" spans="2:6">
@@ -4486,16 +4612,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="E5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="2:6">
@@ -4503,16 +4629,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="E6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="2:6">
@@ -4520,16 +4646,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="E7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="2:6">
@@ -4537,16 +4663,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="E8" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="2:6">
@@ -4554,16 +4680,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="2:6">
@@ -4571,16 +4697,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="2:6">
@@ -4588,16 +4714,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="E11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="2:6">
@@ -4605,16 +4731,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="E12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="2:6">
@@ -4622,16 +4748,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="E13" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="2:6">
@@ -4639,16 +4765,16 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E14" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:6">
@@ -4656,16 +4782,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E15" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="2:6">
@@ -4673,16 +4799,16 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="E16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:6">
@@ -4690,16 +4816,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E17" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="2:6">
@@ -4707,16 +4833,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="E18" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:6">
@@ -4724,16 +4850,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" ht="14.25" spans="2:6">
@@ -4741,16 +4867,16 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E20" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:6">
@@ -4758,16 +4884,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E21" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" ht="14.25" spans="2:6">
@@ -4775,16 +4901,16 @@
         <v>21</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E22" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:6">
@@ -4792,16 +4918,16 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E23" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" ht="14.25" spans="2:6">
@@ -4809,16 +4935,16 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E24" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:6">
@@ -4826,16 +4952,16 @@
         <v>24</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E25" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" ht="14.25" spans="2:6">
@@ -4843,16 +4969,16 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="E26" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:6">
@@ -4860,16 +4986,16 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="E27" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" ht="14.25" spans="2:6">
@@ -4877,16 +5003,16 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E28" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:6">
@@ -4894,16 +5020,16 @@
         <v>28</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E29" s="5" t="b">
         <v>0</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" ht="14.25" spans="2:6">
@@ -4911,16 +5037,16 @@
         <v>29</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E30" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:6">
@@ -4928,16 +5054,16 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E31" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" ht="14.25" spans="2:6">
@@ -4945,16 +5071,16 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="E32" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:6">
@@ -4962,16 +5088,16 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="E33" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" ht="14.25" spans="2:6">
@@ -4979,16 +5105,16 @@
         <v>33</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="E34" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" ht="14.25" spans="2:6">
@@ -4996,16 +5122,16 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="E35" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" ht="14.25" spans="2:6">
@@ -5013,16 +5139,16 @@
         <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="E36" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" ht="14.25" spans="2:6">
@@ -5030,16 +5156,16 @@
         <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="E37" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" ht="14.25" spans="2:6">
@@ -5047,16 +5173,16 @@
         <v>37</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="E38" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" ht="14.25" spans="2:6">
@@ -5064,16 +5190,16 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E39" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" ht="14.25" spans="2:6">
@@ -5081,16 +5207,16 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="E40" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="2:6">
@@ -5098,16 +5224,16 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="E41" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" ht="14.25" spans="2:6">
@@ -5115,16 +5241,16 @@
         <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="E42" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" ht="14.25" spans="2:6">
@@ -5132,16 +5258,16 @@
         <v>42</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E43" s="5" t="b">
         <v>1</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" ht="14.25" spans="2:6">
@@ -5149,16 +5275,16 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="E44" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" ht="14.25" spans="2:6">
@@ -5166,16 +5292,16 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="E45" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" ht="14.25" spans="2:6">
@@ -5183,16 +5309,16 @@
         <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="E46" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" ht="14.25" spans="2:6">
@@ -5200,16 +5326,16 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="E47" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48" ht="14.25" spans="2:6">
@@ -5217,16 +5343,16 @@
         <v>47</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E48" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" ht="14.25" spans="2:6">
@@ -5234,16 +5360,16 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="E49" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" ht="14.25" spans="2:6">
@@ -5251,16 +5377,16 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="E50" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" ht="14.25" spans="2:6">
@@ -5268,16 +5394,16 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E51" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" ht="14.25" spans="2:6">
@@ -5285,16 +5411,16 @@
         <v>51</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E52" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="53" ht="14.25" spans="2:6">
@@ -5302,16 +5428,16 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="E53" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" ht="14.25" spans="2:6">
@@ -5319,16 +5445,16 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="E54" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55" ht="14.25" spans="2:6">
@@ -5336,16 +5462,16 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E55" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" ht="14.25" spans="2:6">
@@ -5353,16 +5479,16 @@
         <v>55</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E56" s="5" t="b">
         <v>0</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" ht="14.25" spans="2:6">
@@ -5370,16 +5496,16 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="E57" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" ht="14.25" spans="2:6">
@@ -5387,16 +5513,16 @@
         <v>57</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="E58" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59" ht="14.25" spans="2:6">
@@ -5404,16 +5530,16 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="E59" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" ht="14.25" spans="2:6">
@@ -5421,7 +5547,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>6</v>
@@ -5430,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" ht="14.25" spans="2:6">
@@ -5438,16 +5564,16 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E61" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" ht="14.25" spans="2:6">
@@ -5455,16 +5581,16 @@
         <v>61</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="E62" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" ht="14.25" spans="2:6">
@@ -5472,16 +5598,16 @@
         <v>62</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="E63" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" ht="14.25" spans="2:6">
@@ -5489,16 +5615,16 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="E64" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" ht="14.25" spans="2:6">
@@ -5506,16 +5632,16 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="E65" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" ht="14.25" spans="2:6">
@@ -5523,16 +5649,16 @@
         <v>65</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="E66" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="67" ht="14.25" spans="2:6">
@@ -5540,16 +5666,16 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="E67" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" ht="14.25" spans="2:6">
@@ -5557,16 +5683,16 @@
         <v>67</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="E68" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="69" ht="14.25" spans="2:6">
@@ -5574,16 +5700,16 @@
         <v>68</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="E69" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" ht="14.25" spans="2:6">
@@ -5591,16 +5717,16 @@
         <v>69</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="E70" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" ht="14.25" spans="2:6">
@@ -5608,16 +5734,16 @@
         <v>70</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="E71" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" ht="14.25" spans="2:6">
@@ -5625,16 +5751,16 @@
         <v>71</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="E72" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" ht="14.25" spans="2:6">
@@ -5642,16 +5768,16 @@
         <v>72</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E73" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" ht="14.25" spans="2:6">
@@ -5659,16 +5785,16 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="E74" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" ht="14.25" spans="2:6">
@@ -5676,14 +5802,14 @@
         <v>74</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" ht="14.25" spans="2:6">
@@ -5691,16 +5817,16 @@
         <v>75</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="E76" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" ht="14.25" spans="2:6">
@@ -5708,16 +5834,16 @@
         <v>76</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="E77" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" ht="14.25" spans="2:6">
@@ -5725,16 +5851,16 @@
         <v>77</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="E78" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="79" ht="14.25" spans="2:6">
@@ -5742,16 +5868,16 @@
         <v>78</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="E79" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" ht="14.25" spans="2:6">
@@ -5759,16 +5885,16 @@
         <v>79</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="E80" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" ht="14.25" spans="2:6">
@@ -5776,16 +5902,16 @@
         <v>80</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="E81" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" ht="14.25" spans="2:6">
@@ -5793,16 +5919,16 @@
         <v>81</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="E82" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" ht="14.25" spans="2:6">
@@ -5810,16 +5936,16 @@
         <v>82</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E83" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" ht="14.25" spans="2:6">
@@ -5827,16 +5953,16 @@
         <v>83</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="E84" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="85" ht="14.25" spans="2:6">
@@ -5844,16 +5970,16 @@
         <v>84</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="E85" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" ht="14.25" spans="2:6">
@@ -5861,16 +5987,16 @@
         <v>85</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="E86" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" ht="14.25" spans="2:6">
@@ -5878,16 +6004,16 @@
         <v>86</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="E87" s="5" t="b">
         <v>1</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="88" ht="14.25" spans="2:6">
@@ -5895,16 +6021,16 @@
         <v>87</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="E88" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89" ht="14.25" spans="2:6">
@@ -5912,16 +6038,16 @@
         <v>88</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="E89" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90" ht="14.25" spans="2:6">
@@ -5929,16 +6055,16 @@
         <v>89</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="E90" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" ht="14.25" spans="2:6">
@@ -5946,16 +6072,16 @@
         <v>90</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="E91" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" ht="14.25" spans="2:6">
@@ -5963,7 +6089,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>6</v>
@@ -5972,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" ht="14.25" spans="2:6">
@@ -5980,16 +6106,16 @@
         <v>92</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E93" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" ht="14.25" spans="2:6">
@@ -5997,21 +6123,21 @@
         <v>93</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="E94" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="C95" s="6" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
